--- a/number.xlsx
+++ b/number.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI_Programs\Selenium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE9AA12-A86F-4BF3-B1B7-A4172080CED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54B2ABC-D372-4EE4-A1A2-F66CADD784BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3810" yWindow="3810" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,13 +36,13 @@
     <t>Junaid</t>
   </si>
   <si>
-    <t>lala</t>
-  </si>
-  <si>
     <t>Faisal</t>
   </si>
   <si>
-    <t>peliw</t>
+    <t>Junaid2</t>
+  </si>
+  <si>
+    <t>Unknown</t>
   </si>
 </sst>
 </file>
@@ -385,7 +385,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>6005852514</v>
@@ -393,7 +393,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -401,7 +401,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>94</v>
+        <v>989825</v>
       </c>
     </row>
   </sheetData>

--- a/number.xlsx
+++ b/number.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI_Programs\Selenium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54B2ABC-D372-4EE4-A1A2-F66CADD784BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF293B7-CBC4-4146-B278-8428EEAB4B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3810" yWindow="3810" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Name</t>
   </si>
@@ -33,16 +33,28 @@
     <t>Number</t>
   </si>
   <si>
-    <t>Junaid</t>
-  </si>
-  <si>
     <t>Faisal</t>
   </si>
   <si>
-    <t>Junaid2</t>
-  </si>
-  <si>
     <t>Unknown</t>
+  </si>
+  <si>
+    <t>060058 52514</t>
+  </si>
+  <si>
+    <t>lala</t>
+  </si>
+  <si>
+    <t>9160058525   14</t>
+  </si>
+  <si>
+    <t>pinklo</t>
+  </si>
+  <si>
+    <t>Junaid_ist</t>
+  </si>
+  <si>
+    <t>Junaid_2nd</t>
   </si>
 </sst>
 </file>
@@ -360,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -377,31 +389,50 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>916005852514</v>
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
-        <v>6005852514</v>
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>9082500</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>989825</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>9809809098809</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>6005852514</v>
       </c>
     </row>
   </sheetData>
